--- a/backend/data/financials_by_company/1298.HK.xlsx
+++ b/backend/data/financials_by_company/1298.HK.xlsx
@@ -4003,7 +4003,7 @@
         <v>-898000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0.795</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0.07179998999999999</v>
